--- a/artfynd/A 23296-2025 artfynd.xlsx
+++ b/artfynd/A 23296-2025 artfynd.xlsx
@@ -675,54 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114358472</v>
+        <v>117866410</v>
       </c>
       <c r="B2" t="n">
-        <v>56470</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Patronssvedberget, Mpd</t>
+          <t>Frölandsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617230</v>
+        <v>617330</v>
       </c>
       <c r="R2" t="n">
-        <v>6934637</v>
+        <v>6934683</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,12 +774,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -784,16 +789,11 @@
         <v>114358474</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -886,12 +886,7 @@
         <v>114358473</v>
       </c>
       <c r="B4" t="n">
-        <v>79586</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,54 +980,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117866410</v>
+        <v>114358472</v>
       </c>
       <c r="B5" t="n">
-        <v>90517</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Frölandsbodarna, Mpd</t>
+          <t>Patronssvedberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617330</v>
+        <v>617230</v>
       </c>
       <c r="R5" t="n">
-        <v>6934683</v>
+        <v>6934637</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1059,22 +1049,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,12 +1069,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 23296-2025 artfynd.xlsx
+++ b/artfynd/A 23296-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117866410</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358474</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358473</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,8 +1098,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358472</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>